--- a/Team-Data/2011-12/1-28-2011-12.xlsx
+++ b/Team-Data/2011-12/1-28-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>3</v>
@@ -763,7 +830,7 @@
         <v>9</v>
       </c>
       <c r="AL2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM2" t="n">
         <v>18</v>
@@ -775,13 +842,13 @@
         <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
         <v>5</v>
@@ -796,10 +863,10 @@
         <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>1.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
         <v>17</v>
@@ -987,16 +1054,16 @@
         <v>27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
         <v>25</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -1025,88 +1092,88 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="H4" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="J4" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.426</v>
+        <v>0.424</v>
       </c>
       <c r="L4" t="n">
         <v>4.3</v>
       </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.305</v>
+        <v>0.303</v>
       </c>
       <c r="O4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P4" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.731</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T4" t="n">
         <v>40.7</v>
       </c>
       <c r="U4" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="V4" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W4" t="n">
         <v>6.1</v>
       </c>
       <c r="X4" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>88.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-11.7</v>
+        <v>-12.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
         <v>30</v>
@@ -1115,16 +1182,16 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI4" t="n">
         <v>19</v>
       </c>
-      <c r="AI4" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ4" t="n">
         <v>10</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>25</v>
@@ -1136,40 +1203,40 @@
         <v>25</v>
       </c>
       <c r="AO4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP4" t="n">
         <v>26</v>
       </c>
-      <c r="AP4" t="n">
-        <v>25</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
         <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>19</v>
@@ -1178,7 +1245,7 @@
         <v>26</v>
       </c>
       <c r="BC4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK5" t="n">
         <v>7</v>
@@ -1324,7 +1391,7 @@
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR5" t="n">
         <v>2</v>
@@ -1339,16 +1406,16 @@
         <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW5" t="n">
         <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
@@ -1357,7 +1424,7 @@
         <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>-3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF6" t="n">
         <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
         <v>11</v>
@@ -1485,7 +1552,7 @@
         <v>17</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK6" t="n">
         <v>20</v>
@@ -1518,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="AU6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV6" t="n">
         <v>30</v>
@@ -1527,7 +1594,7 @@
         <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY6" t="n">
         <v>30</v>
@@ -1536,10 +1603,10 @@
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1658,13 +1725,13 @@
         <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
         <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
         <v>20</v>
@@ -1673,13 +1740,13 @@
         <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>14</v>
@@ -1688,13 +1755,13 @@
         <v>15</v>
       </c>
       <c r="AQ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR7" t="n">
         <v>20</v>
       </c>
-      <c r="AR7" t="n">
-        <v>21</v>
-      </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1858,7 +1925,7 @@
         <v>9</v>
       </c>
       <c r="AM8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>16</v>
@@ -1870,16 +1937,16 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS8" t="n">
         <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -1935,64 +2002,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="J9" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.421</v>
+        <v>0.424</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.361</v>
+        <v>0.365</v>
       </c>
       <c r="O9" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="P9" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R9" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S9" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>38.4</v>
+        <v>38.1</v>
       </c>
       <c r="U9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="V9" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="W9" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
         <v>3.8</v>
@@ -2001,31 +2068,31 @@
         <v>5.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="AA9" t="n">
         <v>18.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>85.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10</v>
+        <v>-9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>30</v>
@@ -2034,7 +2101,7 @@
         <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>24</v>
@@ -2049,7 +2116,7 @@
         <v>20</v>
       </c>
       <c r="AP9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ9" t="n">
         <v>8</v>
@@ -2070,7 +2137,7 @@
         <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>30</v>
@@ -2082,13 +2149,13 @@
         <v>7</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
         <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -2195,16 +2262,16 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
         <v>11</v>
@@ -2213,13 +2280,13 @@
         <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK10" t="n">
         <v>6</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM10" t="n">
         <v>12</v>
@@ -2237,7 +2304,7 @@
         <v>27</v>
       </c>
       <c r="AR10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS10" t="n">
         <v>23</v>
@@ -2249,7 +2316,7 @@
         <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.579</v>
       </c>
       <c r="H11" t="n">
         <v>48.8</v>
@@ -2317,79 +2384,79 @@
         <v>38.4</v>
       </c>
       <c r="J11" t="n">
-        <v>85.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M11" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="N11" t="n">
         <v>0.325</v>
       </c>
       <c r="O11" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="P11" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.802</v>
+        <v>0.803</v>
       </c>
       <c r="R11" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
         <v>20.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z11" t="n">
         <v>20.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2401,7 +2468,7 @@
         <v>14</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AM11" t="n">
         <v>5</v>
@@ -2410,7 +2477,7 @@
         <v>19</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP11" t="n">
         <v>30</v>
@@ -2419,16 +2486,16 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
@@ -2440,7 +2507,7 @@
         <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
         <v>16</v>
@@ -2452,7 +2519,7 @@
         <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2577,10 +2644,10 @@
         <v>24</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>23</v>
@@ -2601,7 +2668,7 @@
         <v>2</v>
       </c>
       <c r="AR12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
         <v>6</v>
@@ -2610,13 +2677,13 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV12" t="n">
         <v>17</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>7</v>
@@ -2628,13 +2695,13 @@
         <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2811,7 @@
         <v>30</v>
       </c>
       <c r="AE13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF13" t="n">
         <v>5</v>
@@ -2762,13 +2829,13 @@
         <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL13" t="n">
         <v>6</v>
       </c>
       <c r="AM13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN13" t="n">
         <v>14</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS13" t="n">
         <v>26</v>
@@ -2798,7 +2865,7 @@
         <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -2845,97 +2912,97 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
         <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.55</v>
+        <v>0.579</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J14" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.45</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M14" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.272</v>
+        <v>0.27</v>
       </c>
       <c r="O14" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P14" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.74</v>
+        <v>0.744</v>
       </c>
       <c r="R14" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="T14" t="n">
         <v>44.4</v>
       </c>
       <c r="U14" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V14" t="n">
         <v>15</v>
       </c>
       <c r="W14" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X14" t="n">
         <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI14" t="n">
         <v>16</v>
@@ -2962,10 +3029,10 @@
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
@@ -2977,28 +3044,28 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -3027,34 +3094,34 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>0.526</v>
+        <v>0.556</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M15" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="N15" t="n">
         <v>0.313</v>
@@ -3063,55 +3130,55 @@
         <v>16.5</v>
       </c>
       <c r="P15" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.737</v>
+        <v>0.732</v>
       </c>
       <c r="R15" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T15" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U15" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W15" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="X15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AA15" t="n">
         <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>94.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
         <v>16</v>
@@ -3123,10 +3190,10 @@
         <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>29</v>
@@ -3135,52 +3202,52 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
         <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB15" t="n">
         <v>14</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>7.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3311,13 +3378,13 @@
         <v>1</v>
       </c>
       <c r="AL16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="n">
         <v>21</v>
       </c>
       <c r="AN16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3329,10 +3396,10 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3350,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.421</v>
+        <v>0.389</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J17" t="n">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.431</v>
+        <v>0.427</v>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M17" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.312</v>
+        <v>0.315</v>
       </c>
       <c r="O17" t="n">
         <v>14.8</v>
       </c>
       <c r="P17" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.788</v>
+        <v>0.781</v>
       </c>
       <c r="R17" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="S17" t="n">
         <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>40.8</v>
+        <v>41.2</v>
       </c>
       <c r="U17" t="n">
         <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="W17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>4.6</v>
@@ -3457,19 +3524,19 @@
         <v>5.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>93.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3484,22 +3551,22 @@
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM17" t="n">
         <v>7</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
@@ -3508,10 +3575,10 @@
         <v>28</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
         <v>27</v>
@@ -3523,10 +3590,10 @@
         <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
         <v>23</v>
@@ -3535,16 +3602,16 @@
         <v>18</v>
       </c>
       <c r="AZ17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA17" t="n">
         <v>20</v>
       </c>
       <c r="BB17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3672,7 +3739,7 @@
         <v>22</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>7</v>
@@ -3684,7 +3751,7 @@
         <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP18" t="n">
         <v>5</v>
@@ -3693,10 +3760,10 @@
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -3708,7 +3775,7 @@
         <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX18" t="n">
         <v>26</v>
@@ -3726,7 +3793,7 @@
         <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-6.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
         <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3866,7 +3933,7 @@
         <v>12</v>
       </c>
       <c r="AO19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP19" t="n">
         <v>20</v>
@@ -3875,7 +3942,7 @@
         <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3884,19 +3951,19 @@
         <v>28</v>
       </c>
       <c r="AU19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV19" t="n">
         <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>28</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ19" t="n">
         <v>14</v>
@@ -3905,7 +3972,7 @@
         <v>14</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4030,7 +4097,7 @@
         <v>14</v>
       </c>
       <c r="AI20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="n">
         <v>24</v>
@@ -4039,7 +4106,7 @@
         <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
@@ -4054,10 +4121,10 @@
         <v>22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>19</v>
@@ -4069,7 +4136,7 @@
         <v>23</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>0.35</v>
+        <v>0.368</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="J21" t="n">
-        <v>80.7</v>
+        <v>80.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="L21" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M21" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.307</v>
+        <v>0.313</v>
       </c>
       <c r="O21" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="P21" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="R21" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>31.4</v>
+        <v>31.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U21" t="n">
         <v>18.6</v>
       </c>
       <c r="V21" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="W21" t="n">
         <v>9.5</v>
@@ -4185,28 +4252,28 @@
         <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.7</v>
+        <v>94.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>6</v>
@@ -4215,40 +4282,40 @@
         <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
       </c>
       <c r="AN21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU21" t="n">
         <v>24</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>25</v>
       </c>
       <c r="AV21" t="n">
         <v>29</v>
@@ -4257,7 +4324,7 @@
         <v>3</v>
       </c>
       <c r="AX21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY21" t="n">
         <v>16</v>
@@ -4269,10 +4336,10 @@
         <v>5</v>
       </c>
       <c r="BB21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4403,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM22" t="n">
         <v>16</v>
@@ -4421,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4430,7 +4497,7 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4448,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>1.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>7</v>
@@ -4591,13 +4658,13 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>15</v>
       </c>
       <c r="AP23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4615,7 +4682,7 @@
         <v>18</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>27</v>
@@ -4636,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="BC23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
@@ -4683,76 +4750,76 @@
         <v>38.9</v>
       </c>
       <c r="J24" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L24" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="M24" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.389</v>
+        <v>0.379</v>
       </c>
       <c r="O24" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="P24" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.732</v>
+        <v>0.735</v>
       </c>
       <c r="R24" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="T24" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U24" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="V24" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="W24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
         <v>17.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
         <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH24" t="n">
         <v>6</v>
@@ -4761,31 +4828,31 @@
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
         <v>4</v>
       </c>
       <c r="AL24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AM24" t="n">
         <v>19</v>
       </c>
       <c r="AN24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR24" t="n">
         <v>28</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>29</v>
       </c>
       <c r="AS24" t="n">
         <v>1</v>
@@ -4803,10 +4870,10 @@
         <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -4847,94 +4914,94 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.368</v>
+        <v>0.333</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="J25" t="n">
-        <v>80.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.439</v>
+        <v>0.444</v>
       </c>
       <c r="L25" t="n">
         <v>6.2</v>
       </c>
       <c r="M25" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O25" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="P25" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.768</v>
+        <v>0.773</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="V25" t="n">
         <v>15.3</v>
       </c>
       <c r="W25" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z25" t="n">
         <v>19.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>91.2</v>
+        <v>91.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-3.8</v>
+        <v>-4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF25" t="n">
         <v>21</v>
       </c>
       <c r="AG25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
@@ -4943,7 +5010,7 @@
         <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK25" t="n">
         <v>15</v>
@@ -4955,43 +5022,43 @@
         <v>15</v>
       </c>
       <c r="AN25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP25" t="n">
         <v>29</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
         <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW25" t="n">
         <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
         <v>3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5116,16 +5183,16 @@
         <v>11</v>
       </c>
       <c r="AG26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI26" t="n">
         <v>11</v>
       </c>
-      <c r="AH26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>12</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5137,7 +5204,7 @@
         <v>14</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
         <v>8</v>
@@ -5146,13 +5213,13 @@
         <v>12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
         <v>9</v>
       </c>
       <c r="AS26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
         <v>5</v>
@@ -5167,7 +5234,7 @@
         <v>10</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY26" t="n">
         <v>12</v>
@@ -5176,7 +5243,7 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -5211,55 +5278,55 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3</v>
+        <v>0.316</v>
       </c>
       <c r="H27" t="n">
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="J27" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.399</v>
+        <v>0.396</v>
       </c>
       <c r="L27" t="n">
         <v>5.7</v>
       </c>
       <c r="M27" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.281</v>
+        <v>0.276</v>
       </c>
       <c r="O27" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="P27" t="n">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.731</v>
+        <v>0.726</v>
       </c>
       <c r="R27" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="S27" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T27" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="U27" t="n">
         <v>15.7</v>
@@ -5268,34 +5335,34 @@
         <v>15.6</v>
       </c>
       <c r="W27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-11.7</v>
+        <v>-12.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF27" t="n">
         <v>24</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5307,7 +5374,7 @@
         <v>28</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>30</v>
@@ -5316,7 +5383,7 @@
         <v>20</v>
       </c>
       <c r="AM27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AN27" t="n">
         <v>28</v>
@@ -5325,10 +5392,10 @@
         <v>9</v>
       </c>
       <c r="AP27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -5337,34 +5404,34 @@
         <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
         <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>7</v>
@@ -5480,16 +5547,16 @@
         <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>4</v>
       </c>
       <c r="AJ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5504,13 +5571,13 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP28" t="n">
         <v>27</v>
       </c>
       <c r="AQ28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR28" t="n">
         <v>27</v>
@@ -5519,7 +5586,7 @@
         <v>18</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5528,10 +5595,10 @@
         <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>-6.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>29</v>
@@ -5674,7 +5741,7 @@
         <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL29" t="n">
         <v>19</v>
@@ -5689,13 +5756,13 @@
         <v>21</v>
       </c>
       <c r="AP29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
         <v>12</v>
@@ -5713,10 +5780,10 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -5757,94 +5824,94 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.611</v>
+        <v>0.588</v>
       </c>
       <c r="H30" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I30" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.296</v>
+        <v>0.288</v>
       </c>
       <c r="O30" t="n">
         <v>19.4</v>
       </c>
       <c r="P30" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.743</v>
+        <v>0.738</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S30" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="T30" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U30" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="V30" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="W30" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y30" t="n">
         <v>5.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="AA30" t="n">
         <v>21.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF30" t="n">
         <v>9</v>
       </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>3</v>
@@ -5859,10 +5926,10 @@
         <v>8</v>
       </c>
       <c r="AL30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN30" t="n">
         <v>26</v>
@@ -5874,31 +5941,31 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
         <v>17</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU30" t="n">
         <v>16</v>
       </c>
       <c r="AV30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
@@ -5939,112 +6006,112 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>16</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>0.158</v>
       </c>
       <c r="H31" t="n">
         <v>48</v>
       </c>
       <c r="I31" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="J31" t="n">
-        <v>82.8</v>
+        <v>83.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.42</v>
+        <v>0.415</v>
       </c>
       <c r="L31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="M31" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.293</v>
+        <v>0.282</v>
       </c>
       <c r="O31" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
         <v>21.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.724</v>
+        <v>0.722</v>
       </c>
       <c r="R31" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="S31" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>42.1</v>
       </c>
       <c r="U31" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="V31" t="n">
         <v>15.8</v>
       </c>
       <c r="W31" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>88.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-9.4</v>
+        <v>-10.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
         <v>28</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
         <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN31" t="n">
         <v>27</v>
@@ -6059,40 +6126,40 @@
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AU31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX31" t="n">
         <v>1</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
         <v>27</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-28-2011-12</t>
+          <t>2012-01-28</t>
         </is>
       </c>
     </row>
